--- a/public/PlantillaCargueContactosPersonalizados.xlsx
+++ b/public/PlantillaCargueContactosPersonalizados.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MEN\Masivas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/05668193c6fed33f/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE240FC1-BCD2-4971-8686-F4A5F42BC484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{BE240FC1-BCD2-4971-8686-F4A5F42BC484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6C486B1-9AC7-4B09-8FD0-98BE2D88642D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -250,7 +250,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2354" uniqueCount="1146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2360" uniqueCount="1152">
   <si>
     <t>Tratamiento</t>
   </si>
@@ -3688,16 +3688,41 @@
   </si>
   <si>
     <t>Teniente Coronel</t>
+  </si>
+  <si>
+    <t>Rector </t>
+  </si>
+  <si>
+    <t>Rectora </t>
+  </si>
+  <si>
+    <t>Docente </t>
+  </si>
+  <si>
+    <t>Maestro </t>
+  </si>
+  <si>
+    <t>Maestra </t>
+  </si>
+  <si>
+    <t>Estudiante</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3807,6 +3832,11 @@
     <font>
       <sz val="9"/>
       <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -3965,31 +3995,31 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3998,42 +4028,50 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4054,6 +4092,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8039,11 +8081,11 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9FE20749-750A-44CC-BA64-EC67BF475001}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{24F3F1EE-2406-4BDD-9179-C6DCCEEAF284}">
           <x14:formula1>
-            <xm:f>Datos!$B$3:$B$61</xm:f>
+            <xm:f>Datos!$B$3:$B$67</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A103 A113:A1048576</xm:sqref>
+          <xm:sqref>A2:A1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8062,27 +8104,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="15.75" thickBot="1">
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="2:4">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="24" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="2:4" ht="15.75" thickBot="1">
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
     </row>
     <row r="4" spans="2:4" ht="92.25" customHeight="1" thickBot="1">
       <c r="B4" s="6" t="s">
@@ -11578,7 +11620,7 @@
       <c r="A421" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="B421" s="4" t="s">
+      <c r="B421" s="23" t="s">
         <v>441</v>
       </c>
     </row>
@@ -17222,7 +17264,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{041FFBD1-E305-4C3C-BF52-C53CB58561C4}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="B2:B61"/>
+  <dimension ref="B2:B73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24.140625" customWidth="1"/>
@@ -17527,6 +17569,48 @@
       <c r="B61" s="2" t="s">
         <v>1145</v>
       </c>
+    </row>
+    <row r="62" spans="2:2" ht="16.5">
+      <c r="B62" s="31" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" ht="16.5">
+      <c r="B63" s="31" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" ht="16.5">
+      <c r="B64" s="31" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" ht="16.5">
+      <c r="B65" s="31" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" ht="16.5">
+      <c r="B66" s="31" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" ht="16.5">
+      <c r="B67" s="31" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" ht="16.5">
+      <c r="B69" s="29"/>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="30"/>
+    </row>
+    <row r="72" spans="2:2" ht="16.5">
+      <c r="B72" s="29"/>
+    </row>
+    <row r="73" spans="2:2" ht="16.5">
+      <c r="B73" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
